--- a/output/reports/本番_保育園欠席分析報告書.xlsx
+++ b/output/reports/本番_保育園欠席分析報告書.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-168" yWindow="432" windowWidth="11868" windowHeight="12816" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId1"/>
@@ -293,104 +293,104 @@
   <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -967,7 +967,7 @@
   <dimension ref="C12:AB44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="11" ht="15" customHeight="1" thickBot="1"/>
@@ -1048,7 +1048,7 @@
       <c r="AB17" s="47" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J44" s="22" t="inlineStr">
         <is>
           <t>2026/07/03</t>
         </is>
@@ -1073,11 +1073,11 @@
   <dimension ref="B2:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>3.総合所見</t>
         </is>
@@ -1085,95 +1085,95 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>AIによる予測では、対象児童2名の平均欠席日数は約1.6日と推定された。全員が予測期間内に安定化すると予測され、現在の健康管理を継続することが望まれる。</t>
         </is>
       </c>
-      <c r="C4" s="34" t="n"/>
-      <c r="D4" s="34" t="n"/>
-      <c r="E4" s="34" t="n"/>
-      <c r="F4" s="34" t="n"/>
-      <c r="G4" s="34" t="n"/>
-      <c r="H4" s="34" t="n"/>
-      <c r="I4" s="34" t="n"/>
-      <c r="J4" s="34" t="n"/>
-      <c r="K4" s="34" t="n"/>
-      <c r="L4" s="34" t="n"/>
-      <c r="M4" s="34" t="n"/>
-      <c r="N4" s="34" t="n"/>
-      <c r="O4" s="34" t="n"/>
-      <c r="P4" s="34" t="n"/>
-      <c r="Q4" s="34" t="n"/>
-      <c r="R4" s="34" t="n"/>
-      <c r="S4" s="34" t="n"/>
-      <c r="T4" s="34" t="n"/>
-      <c r="U4" s="34" t="n"/>
-      <c r="V4" s="34" t="n"/>
-      <c r="W4" s="34" t="n"/>
-      <c r="X4" s="34" t="n"/>
-      <c r="Y4" s="34" t="n"/>
-      <c r="Z4" s="34" t="n"/>
-      <c r="AA4" s="34" t="n"/>
-      <c r="AB4" s="34" t="n"/>
-      <c r="AC4" s="35" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" s="4" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="36" t="n"/>
-      <c r="AC5" s="37" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="AC5" s="7" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="36" t="n"/>
-      <c r="AC6" s="37" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="AC6" s="7" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="36" t="n"/>
-      <c r="AC7" s="37" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="AC7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="36" t="n"/>
-      <c r="AC8" s="37" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="AC8" s="7" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="36" t="n"/>
-      <c r="AC9" s="37" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="AC9" s="7" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="36" t="n"/>
-      <c r="AC10" s="37" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="AC10" s="7" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="38" t="n"/>
-      <c r="C11" s="32" t="n"/>
-      <c r="D11" s="32" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="32" t="n"/>
-      <c r="G11" s="32" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="32" t="n"/>
-      <c r="J11" s="32" t="n"/>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="32" t="n"/>
-      <c r="M11" s="32" t="n"/>
-      <c r="N11" s="32" t="n"/>
-      <c r="O11" s="32" t="n"/>
-      <c r="P11" s="32" t="n"/>
-      <c r="Q11" s="32" t="n"/>
-      <c r="R11" s="32" t="n"/>
-      <c r="S11" s="32" t="n"/>
-      <c r="T11" s="32" t="n"/>
-      <c r="U11" s="32" t="n"/>
-      <c r="V11" s="32" t="n"/>
-      <c r="W11" s="32" t="n"/>
-      <c r="X11" s="32" t="n"/>
-      <c r="Y11" s="32" t="n"/>
-      <c r="Z11" s="32" t="n"/>
-      <c r="AA11" s="32" t="n"/>
-      <c r="AB11" s="32" t="n"/>
-      <c r="AC11" s="39" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="9" t="n"/>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="9" t="n"/>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="9" t="n"/>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="9" t="n"/>
+      <c r="AC11" s="10" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>4.結論</t>
         </is>
@@ -1181,92 +1181,92 @@
     </row>
     <row r="15" ht="15" customHeight="1"/>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>AI予測では対象児童2名中2名で予測期間内の安定化が見込まれた。最も早い児童は約5か月後に安定すると予測された。今後も健康観察と家庭との情報共有を継続し、児童ごとの状況に応じた支援を行うことが望まれる。</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="n"/>
-      <c r="E16" s="34" t="n"/>
-      <c r="F16" s="34" t="n"/>
-      <c r="G16" s="34" t="n"/>
-      <c r="H16" s="34" t="n"/>
-      <c r="I16" s="34" t="n"/>
-      <c r="J16" s="34" t="n"/>
-      <c r="K16" s="34" t="n"/>
-      <c r="L16" s="34" t="n"/>
-      <c r="M16" s="34" t="n"/>
-      <c r="N16" s="34" t="n"/>
-      <c r="O16" s="34" t="n"/>
-      <c r="P16" s="34" t="n"/>
-      <c r="Q16" s="34" t="n"/>
-      <c r="R16" s="34" t="n"/>
-      <c r="S16" s="34" t="n"/>
-      <c r="T16" s="34" t="n"/>
-      <c r="U16" s="34" t="n"/>
-      <c r="V16" s="34" t="n"/>
-      <c r="W16" s="34" t="n"/>
-      <c r="X16" s="34" t="n"/>
-      <c r="Y16" s="34" t="n"/>
-      <c r="Z16" s="34" t="n"/>
-      <c r="AA16" s="34" t="n"/>
-      <c r="AB16" s="34" t="n"/>
-      <c r="AC16" s="35" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="3" t="n"/>
+      <c r="Q16" s="3" t="n"/>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="n"/>
+      <c r="U16" s="3" t="n"/>
+      <c r="V16" s="3" t="n"/>
+      <c r="W16" s="3" t="n"/>
+      <c r="X16" s="3" t="n"/>
+      <c r="Y16" s="3" t="n"/>
+      <c r="Z16" s="3" t="n"/>
+      <c r="AA16" s="3" t="n"/>
+      <c r="AB16" s="3" t="n"/>
+      <c r="AC16" s="4" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="36" t="n"/>
-      <c r="AC17" s="37" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="AC17" s="7" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="36" t="n"/>
-      <c r="AC18" s="37" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="AC18" s="7" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="36" t="n"/>
-      <c r="AC19" s="37" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="AC19" s="7" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="36" t="n"/>
-      <c r="AC20" s="37" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="AC20" s="7" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="36" t="n"/>
-      <c r="AC21" s="37" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="AC21" s="7" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="36" t="n"/>
-      <c r="AC22" s="37" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="AC22" s="7" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="38" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="32" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="32" t="n"/>
-      <c r="M23" s="32" t="n"/>
-      <c r="N23" s="32" t="n"/>
-      <c r="O23" s="32" t="n"/>
-      <c r="P23" s="32" t="n"/>
-      <c r="Q23" s="32" t="n"/>
-      <c r="R23" s="32" t="n"/>
-      <c r="S23" s="32" t="n"/>
-      <c r="T23" s="32" t="n"/>
-      <c r="U23" s="32" t="n"/>
-      <c r="V23" s="32" t="n"/>
-      <c r="W23" s="32" t="n"/>
-      <c r="X23" s="32" t="n"/>
-      <c r="Y23" s="32" t="n"/>
-      <c r="Z23" s="32" t="n"/>
-      <c r="AA23" s="32" t="n"/>
-      <c r="AB23" s="32" t="n"/>
-      <c r="AC23" s="39" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="9" t="n"/>
+      <c r="O23" s="9" t="n"/>
+      <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="9" t="n"/>
+      <c r="S23" s="9" t="n"/>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="9" t="n"/>
+      <c r="V23" s="9" t="n"/>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="9" t="n"/>
+      <c r="Y23" s="9" t="n"/>
+      <c r="Z23" s="9" t="n"/>
+      <c r="AA23" s="9" t="n"/>
+      <c r="AB23" s="9" t="n"/>
+      <c r="AC23" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1289,7 +1289,7 @@
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1306,11 +1306,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>1-1.目的</t>
         </is>
@@ -1318,80 +1318,80 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>保育園における園児の欠席傾向を分析し、
 業務改善および将来リスク予測に活用する。</t>
         </is>
       </c>
-      <c r="C5" s="34" t="n"/>
-      <c r="D5" s="34" t="n"/>
-      <c r="E5" s="34" t="n"/>
-      <c r="F5" s="34" t="n"/>
-      <c r="G5" s="34" t="n"/>
-      <c r="H5" s="34" t="n"/>
-      <c r="I5" s="34" t="n"/>
-      <c r="J5" s="34" t="n"/>
-      <c r="K5" s="34" t="n"/>
-      <c r="L5" s="34" t="n"/>
-      <c r="M5" s="34" t="n"/>
-      <c r="N5" s="34" t="n"/>
-      <c r="O5" s="34" t="n"/>
-      <c r="P5" s="34" t="n"/>
-      <c r="Q5" s="34" t="n"/>
-      <c r="R5" s="34" t="n"/>
-      <c r="S5" s="34" t="n"/>
-      <c r="T5" s="34" t="n"/>
-      <c r="U5" s="34" t="n"/>
-      <c r="V5" s="34" t="n"/>
-      <c r="W5" s="34" t="n"/>
-      <c r="X5" s="34" t="n"/>
-      <c r="Y5" s="34" t="n"/>
-      <c r="Z5" s="34" t="n"/>
-      <c r="AA5" s="34" t="n"/>
-      <c r="AB5" s="34" t="n"/>
-      <c r="AC5" s="35" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" s="3" t="n"/>
+      <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
+      <c r="AB5" s="3" t="n"/>
+      <c r="AC5" s="4" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="36" t="n"/>
-      <c r="AC6" s="37" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="AC6" s="7" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="36" t="n"/>
-      <c r="AC7" s="37" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="AC7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="38" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="32" t="n"/>
-      <c r="J8" s="32" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="32" t="n"/>
-      <c r="M8" s="32" t="n"/>
-      <c r="N8" s="32" t="n"/>
-      <c r="O8" s="32" t="n"/>
-      <c r="P8" s="32" t="n"/>
-      <c r="Q8" s="32" t="n"/>
-      <c r="R8" s="32" t="n"/>
-      <c r="S8" s="32" t="n"/>
-      <c r="T8" s="32" t="n"/>
-      <c r="U8" s="32" t="n"/>
-      <c r="V8" s="32" t="n"/>
-      <c r="W8" s="32" t="n"/>
-      <c r="X8" s="32" t="n"/>
-      <c r="Y8" s="32" t="n"/>
-      <c r="Z8" s="32" t="n"/>
-      <c r="AA8" s="32" t="n"/>
-      <c r="AB8" s="32" t="n"/>
-      <c r="AC8" s="39" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
+      <c r="R8" s="9" t="n"/>
+      <c r="S8" s="9" t="n"/>
+      <c r="T8" s="9" t="n"/>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
+      <c r="W8" s="9" t="n"/>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="9" t="n"/>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="10" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>1-2.対象データ</t>
         </is>
@@ -1399,81 +1399,81 @@
     </row>
     <row r="11" ht="15" customHeight="1"/>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>・子供001(2020年生まれ・女)
 ・子供002(2021年生まれ・男)
 ・期間：2021年〜2026年</t>
         </is>
       </c>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="34" t="n"/>
-      <c r="E13" s="34" t="n"/>
-      <c r="F13" s="34" t="n"/>
-      <c r="G13" s="34" t="n"/>
-      <c r="H13" s="34" t="n"/>
-      <c r="I13" s="34" t="n"/>
-      <c r="J13" s="34" t="n"/>
-      <c r="K13" s="34" t="n"/>
-      <c r="L13" s="34" t="n"/>
-      <c r="M13" s="34" t="n"/>
-      <c r="N13" s="34" t="n"/>
-      <c r="O13" s="34" t="n"/>
-      <c r="P13" s="34" t="n"/>
-      <c r="Q13" s="34" t="n"/>
-      <c r="R13" s="34" t="n"/>
-      <c r="S13" s="34" t="n"/>
-      <c r="T13" s="34" t="n"/>
-      <c r="U13" s="34" t="n"/>
-      <c r="V13" s="34" t="n"/>
-      <c r="W13" s="34" t="n"/>
-      <c r="X13" s="34" t="n"/>
-      <c r="Y13" s="34" t="n"/>
-      <c r="Z13" s="34" t="n"/>
-      <c r="AA13" s="34" t="n"/>
-      <c r="AB13" s="34" t="n"/>
-      <c r="AC13" s="35" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="n"/>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3" t="n"/>
+      <c r="W13" s="3" t="n"/>
+      <c r="X13" s="3" t="n"/>
+      <c r="Y13" s="3" t="n"/>
+      <c r="Z13" s="3" t="n"/>
+      <c r="AA13" s="3" t="n"/>
+      <c r="AB13" s="3" t="n"/>
+      <c r="AC13" s="4" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="36" t="n"/>
-      <c r="AC14" s="37" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="AC14" s="7" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="36" t="n"/>
-      <c r="AC15" s="37" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="AC15" s="7" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="38" t="n"/>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="n"/>
-      <c r="G16" s="32" t="n"/>
-      <c r="H16" s="32" t="n"/>
-      <c r="I16" s="32" t="n"/>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="n"/>
-      <c r="M16" s="32" t="n"/>
-      <c r="N16" s="32" t="n"/>
-      <c r="O16" s="32" t="n"/>
-      <c r="P16" s="32" t="n"/>
-      <c r="Q16" s="32" t="n"/>
-      <c r="R16" s="32" t="n"/>
-      <c r="S16" s="32" t="n"/>
-      <c r="T16" s="32" t="n"/>
-      <c r="U16" s="32" t="n"/>
-      <c r="V16" s="32" t="n"/>
-      <c r="W16" s="32" t="n"/>
-      <c r="X16" s="32" t="n"/>
-      <c r="Y16" s="32" t="n"/>
-      <c r="Z16" s="32" t="n"/>
-      <c r="AA16" s="32" t="n"/>
-      <c r="AB16" s="32" t="n"/>
-      <c r="AC16" s="39" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="9" t="n"/>
+      <c r="S16" s="9" t="n"/>
+      <c r="T16" s="9" t="n"/>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="9" t="n"/>
+      <c r="W16" s="9" t="n"/>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
+      <c r="Z16" s="9" t="n"/>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="9" t="n"/>
+      <c r="AC16" s="10" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>1-3.使用手法</t>
         </is>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="19" ht="15" customHeight="1"/>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>・統計分析
 ・時系列分析
@@ -1489,79 +1489,79 @@
 ・リスク予測シミュレーション</t>
         </is>
       </c>
-      <c r="C21" s="34" t="n"/>
-      <c r="D21" s="34" t="n"/>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="34" t="n"/>
-      <c r="G21" s="34" t="n"/>
-      <c r="H21" s="34" t="n"/>
-      <c r="I21" s="34" t="n"/>
-      <c r="J21" s="34" t="n"/>
-      <c r="K21" s="34" t="n"/>
-      <c r="L21" s="34" t="n"/>
-      <c r="M21" s="34" t="n"/>
-      <c r="N21" s="34" t="n"/>
-      <c r="O21" s="34" t="n"/>
-      <c r="P21" s="34" t="n"/>
-      <c r="Q21" s="34" t="n"/>
-      <c r="R21" s="34" t="n"/>
-      <c r="S21" s="34" t="n"/>
-      <c r="T21" s="34" t="n"/>
-      <c r="U21" s="34" t="n"/>
-      <c r="V21" s="34" t="n"/>
-      <c r="W21" s="34" t="n"/>
-      <c r="X21" s="34" t="n"/>
-      <c r="Y21" s="34" t="n"/>
-      <c r="Z21" s="34" t="n"/>
-      <c r="AA21" s="34" t="n"/>
-      <c r="AB21" s="34" t="n"/>
-      <c r="AC21" s="35" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="3" t="n"/>
+      <c r="U21" s="3" t="n"/>
+      <c r="V21" s="3" t="n"/>
+      <c r="W21" s="3" t="n"/>
+      <c r="X21" s="3" t="n"/>
+      <c r="Y21" s="3" t="n"/>
+      <c r="Z21" s="3" t="n"/>
+      <c r="AA21" s="3" t="n"/>
+      <c r="AB21" s="3" t="n"/>
+      <c r="AC21" s="4" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="36" t="n"/>
-      <c r="AC22" s="37" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="AC22" s="7" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="36" t="n"/>
-      <c r="AC23" s="37" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="AC23" s="7" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="36" t="n"/>
-      <c r="AC24" s="37" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="AC24" s="7" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="36" t="n"/>
-      <c r="AC25" s="37" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="AC25" s="7" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="38" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="32" t="n"/>
-      <c r="G26" s="32" t="n"/>
-      <c r="H26" s="32" t="n"/>
-      <c r="I26" s="32" t="n"/>
-      <c r="J26" s="32" t="n"/>
-      <c r="K26" s="32" t="n"/>
-      <c r="L26" s="32" t="n"/>
-      <c r="M26" s="32" t="n"/>
-      <c r="N26" s="32" t="n"/>
-      <c r="O26" s="32" t="n"/>
-      <c r="P26" s="32" t="n"/>
-      <c r="Q26" s="32" t="n"/>
-      <c r="R26" s="32" t="n"/>
-      <c r="S26" s="32" t="n"/>
-      <c r="T26" s="32" t="n"/>
-      <c r="U26" s="32" t="n"/>
-      <c r="V26" s="32" t="n"/>
-      <c r="W26" s="32" t="n"/>
-      <c r="X26" s="32" t="n"/>
-      <c r="Y26" s="32" t="n"/>
-      <c r="Z26" s="32" t="n"/>
-      <c r="AA26" s="32" t="n"/>
-      <c r="AB26" s="32" t="n"/>
-      <c r="AC26" s="39" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="9" t="n"/>
+      <c r="N26" s="9" t="n"/>
+      <c r="O26" s="9" t="n"/>
+      <c r="P26" s="9" t="n"/>
+      <c r="Q26" s="9" t="n"/>
+      <c r="R26" s="9" t="n"/>
+      <c r="S26" s="9" t="n"/>
+      <c r="T26" s="9" t="n"/>
+      <c r="U26" s="9" t="n"/>
+      <c r="V26" s="9" t="n"/>
+      <c r="W26" s="9" t="n"/>
+      <c r="X26" s="9" t="n"/>
+      <c r="Y26" s="9" t="n"/>
+      <c r="Z26" s="9" t="n"/>
+      <c r="AA26" s="9" t="n"/>
+      <c r="AB26" s="9" t="n"/>
+      <c r="AC26" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1586,11 +1586,11 @@
   <dimension ref="B2:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-1.分析サマリー</t>
         </is>
@@ -1598,226 +1598,226 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>■ 主な傾向</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="32" t="n"/>
-      <c r="C5" s="32" t="n"/>
-      <c r="D5" s="32" t="n"/>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="32" t="n"/>
-      <c r="G5" s="32" t="n"/>
-      <c r="H5" s="32" t="n"/>
-      <c r="I5" s="32" t="n"/>
-      <c r="J5" s="32" t="n"/>
-      <c r="K5" s="32" t="n"/>
-      <c r="L5" s="32" t="n"/>
-      <c r="M5" s="32" t="n"/>
-      <c r="N5" s="32" t="n"/>
-      <c r="O5" s="32" t="n"/>
-      <c r="P5" s="32" t="n"/>
-      <c r="Q5" s="32" t="n"/>
-      <c r="R5" s="32" t="n"/>
-      <c r="S5" s="32" t="n"/>
-      <c r="T5" s="32" t="n"/>
-      <c r="U5" s="32" t="n"/>
-      <c r="V5" s="32" t="n"/>
-      <c r="W5" s="32" t="n"/>
-      <c r="X5" s="32" t="n"/>
-      <c r="Y5" s="32" t="n"/>
-      <c r="Z5" s="32" t="n"/>
-      <c r="AA5" s="32" t="n"/>
-      <c r="AB5" s="32" t="n"/>
-      <c r="AC5" s="32" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="9" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="9" t="n"/>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="9" t="n"/>
+      <c r="AA5" s="9" t="n"/>
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="9" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>【子供001】
-月齢による平均欠席日数の大きな変化は認められなかった。
-学年が上がるにつれて平均欠席日数は約30.0日から約0.0日へ減少した。
-登園月数の経過に伴い平均欠席日数は約4.0日から約0.0日へ減少した。
-登園年数の経過に伴い平均欠席日数は約31.0日から約0.0日へ減少した。
-8月の平均欠席日数が約19.0日と最も高く、季節性の影響がみられた。
-月間推移では平均欠席日数が約2.0日から約0.0日へ減少した。
+月齢による欠席日数の大きな変化は認められなかった。
+学年が上がるにつれて欠席日数は約30.0日から約0.0日へ減少した。
+登園月数の経過に伴い欠席日数は約4.0日から約0.0日へ減少した。
+登園年数の経過に伴い欠席日数は約31.0日から約0.0日へ減少した。
+8月の欠席日数が約19.0日と最も高く、季節性の影響がみられた。
+月間推移では欠席日数が約2.0日から約0.0日へ減少した。
 【子供002】
-月齢による平均欠席日数の大きな変化は認められなかった。
-学年が上がるにつれて平均欠席日数は約15.0日から約0.0日へ減少した。
-登園月数の経過に伴い平均欠席日数は約2.0日から約0.0日へ減少した。
-登園年数の経過に伴い平均欠席日数は約21.0日から約5.0日へ減少した。
-11月の平均欠席日数が約10.0日と最も高く、季節性の影響がみられた。
-月間推移では平均欠席日数が約2.0日から約0.0日へ減少した。</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n"/>
-      <c r="F6" s="34" t="n"/>
-      <c r="G6" s="34" t="n"/>
-      <c r="H6" s="34" t="n"/>
-      <c r="I6" s="34" t="n"/>
-      <c r="J6" s="34" t="n"/>
-      <c r="K6" s="34" t="n"/>
-      <c r="L6" s="34" t="n"/>
-      <c r="M6" s="34" t="n"/>
-      <c r="N6" s="34" t="n"/>
-      <c r="O6" s="34" t="n"/>
-      <c r="P6" s="34" t="n"/>
-      <c r="Q6" s="34" t="n"/>
-      <c r="R6" s="34" t="n"/>
-      <c r="S6" s="34" t="n"/>
-      <c r="T6" s="34" t="n"/>
-      <c r="U6" s="34" t="n"/>
-      <c r="V6" s="34" t="n"/>
-      <c r="W6" s="34" t="n"/>
-      <c r="X6" s="34" t="n"/>
-      <c r="Y6" s="34" t="n"/>
-      <c r="Z6" s="34" t="n"/>
-      <c r="AA6" s="34" t="n"/>
-      <c r="AB6" s="34" t="n"/>
-      <c r="AC6" s="35" t="n"/>
+月齢による欠席日数の大きな変化は認められなかった。
+学年が上がるにつれて欠席日数は約15.0日から約0.0日へ減少した。
+登園月数の経過に伴い欠席日数は約2.0日から約0.0日へ減少した。
+登園年数の経過に伴い欠席日数は約21.0日から約5.0日へ減少した。
+11月の欠席日数が約10.0日と最も高く、季節性の影響がみられた。
+月間推移では欠席日数が約2.0日から約0.0日へ減少した。</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="3" t="n"/>
+      <c r="X6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n"/>
+      <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" s="4" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="36" t="n"/>
-      <c r="AC7" s="37" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="AC7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="36" t="n"/>
-      <c r="AC8" s="37" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="AC8" s="7" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="36" t="n"/>
-      <c r="AC9" s="37" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="AC9" s="7" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="36" t="n"/>
-      <c r="AC10" s="37" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="AC10" s="7" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="36" t="n"/>
-      <c r="AC11" s="37" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="AC11" s="7" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="B12" s="36" t="n"/>
-      <c r="AC12" s="37" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="AC12" s="7" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="36" t="n"/>
-      <c r="AC13" s="37" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="AC13" s="7" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="36" t="n"/>
-      <c r="AC14" s="37" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="AC14" s="7" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="36" t="n"/>
-      <c r="AC15" s="37" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="AC15" s="7" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="36" t="n"/>
-      <c r="AC16" s="37" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="AC16" s="7" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="36" t="n"/>
-      <c r="AC17" s="37" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="AC17" s="7" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="36" t="n"/>
-      <c r="AC18" s="37" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="AC18" s="7" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="36" t="n"/>
-      <c r="AC19" s="37" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="AC19" s="7" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="36" t="n"/>
-      <c r="AC20" s="37" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="AC20" s="7" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="36" t="n"/>
-      <c r="AC21" s="37" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="AC21" s="7" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="36" t="n"/>
-      <c r="AC22" s="37" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="AC22" s="7" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="36" t="n"/>
-      <c r="AC23" s="37" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="AC23" s="7" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="38" t="n"/>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="32" t="n"/>
-      <c r="F24" s="32" t="n"/>
-      <c r="G24" s="32" t="n"/>
-      <c r="H24" s="32" t="n"/>
-      <c r="I24" s="32" t="n"/>
-      <c r="J24" s="32" t="n"/>
-      <c r="K24" s="32" t="n"/>
-      <c r="L24" s="32" t="n"/>
-      <c r="M24" s="32" t="n"/>
-      <c r="N24" s="32" t="n"/>
-      <c r="O24" s="32" t="n"/>
-      <c r="P24" s="32" t="n"/>
-      <c r="Q24" s="32" t="n"/>
-      <c r="R24" s="32" t="n"/>
-      <c r="S24" s="32" t="n"/>
-      <c r="T24" s="32" t="n"/>
-      <c r="U24" s="32" t="n"/>
-      <c r="V24" s="32" t="n"/>
-      <c r="W24" s="32" t="n"/>
-      <c r="X24" s="32" t="n"/>
-      <c r="Y24" s="32" t="n"/>
-      <c r="Z24" s="32" t="n"/>
-      <c r="AA24" s="32" t="n"/>
-      <c r="AB24" s="32" t="n"/>
-      <c r="AC24" s="39" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="9" t="n"/>
+      <c r="S24" s="9" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="9" t="n"/>
+      <c r="V24" s="9" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="9" t="n"/>
+      <c r="Y24" s="9" t="n"/>
+      <c r="Z24" s="9" t="n"/>
+      <c r="AA24" s="9" t="n"/>
+      <c r="AB24" s="9" t="n"/>
+      <c r="AC24" s="10" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>■ 未来予測結果</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="32" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="32" t="n"/>
-      <c r="G26" s="32" t="n"/>
-      <c r="H26" s="32" t="n"/>
-      <c r="I26" s="32" t="n"/>
-      <c r="J26" s="32" t="n"/>
-      <c r="K26" s="32" t="n"/>
-      <c r="L26" s="32" t="n"/>
-      <c r="M26" s="32" t="n"/>
-      <c r="N26" s="32" t="n"/>
-      <c r="O26" s="32" t="n"/>
-      <c r="P26" s="32" t="n"/>
-      <c r="Q26" s="32" t="n"/>
-      <c r="R26" s="32" t="n"/>
-      <c r="S26" s="32" t="n"/>
-      <c r="T26" s="32" t="n"/>
-      <c r="U26" s="32" t="n"/>
-      <c r="V26" s="32" t="n"/>
-      <c r="W26" s="32" t="n"/>
-      <c r="X26" s="32" t="n"/>
-      <c r="Y26" s="32" t="n"/>
-      <c r="Z26" s="32" t="n"/>
-      <c r="AA26" s="32" t="n"/>
-      <c r="AB26" s="32" t="n"/>
-      <c r="AC26" s="32" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="9" t="n"/>
+      <c r="N26" s="9" t="n"/>
+      <c r="O26" s="9" t="n"/>
+      <c r="P26" s="9" t="n"/>
+      <c r="Q26" s="9" t="n"/>
+      <c r="R26" s="9" t="n"/>
+      <c r="S26" s="9" t="n"/>
+      <c r="T26" s="9" t="n"/>
+      <c r="U26" s="9" t="n"/>
+      <c r="V26" s="9" t="n"/>
+      <c r="W26" s="9" t="n"/>
+      <c r="X26" s="9" t="n"/>
+      <c r="Y26" s="9" t="n"/>
+      <c r="Z26" s="9" t="n"/>
+      <c r="AA26" s="9" t="n"/>
+      <c r="AB26" s="9" t="n"/>
+      <c r="AC26" s="9" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>【子供001】
 平均欠席日数は約1.3日と予測された。
@@ -1827,131 +1827,131 @@
 約9か月後に安定基準へ到達すると予測された。</t>
         </is>
       </c>
-      <c r="C27" s="34" t="n"/>
-      <c r="D27" s="34" t="n"/>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="34" t="n"/>
-      <c r="G27" s="34" t="n"/>
-      <c r="H27" s="34" t="n"/>
-      <c r="I27" s="34" t="n"/>
-      <c r="J27" s="34" t="n"/>
-      <c r="K27" s="34" t="n"/>
-      <c r="L27" s="34" t="n"/>
-      <c r="M27" s="34" t="n"/>
-      <c r="N27" s="34" t="n"/>
-      <c r="O27" s="34" t="n"/>
-      <c r="P27" s="34" t="n"/>
-      <c r="Q27" s="34" t="n"/>
-      <c r="R27" s="34" t="n"/>
-      <c r="S27" s="34" t="n"/>
-      <c r="T27" s="34" t="n"/>
-      <c r="U27" s="34" t="n"/>
-      <c r="V27" s="34" t="n"/>
-      <c r="W27" s="34" t="n"/>
-      <c r="X27" s="34" t="n"/>
-      <c r="Y27" s="34" t="n"/>
-      <c r="Z27" s="34" t="n"/>
-      <c r="AA27" s="34" t="n"/>
-      <c r="AB27" s="34" t="n"/>
-      <c r="AC27" s="35" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="n"/>
+      <c r="Q27" s="3" t="n"/>
+      <c r="R27" s="3" t="n"/>
+      <c r="S27" s="3" t="n"/>
+      <c r="T27" s="3" t="n"/>
+      <c r="U27" s="3" t="n"/>
+      <c r="V27" s="3" t="n"/>
+      <c r="W27" s="3" t="n"/>
+      <c r="X27" s="3" t="n"/>
+      <c r="Y27" s="3" t="n"/>
+      <c r="Z27" s="3" t="n"/>
+      <c r="AA27" s="3" t="n"/>
+      <c r="AB27" s="3" t="n"/>
+      <c r="AC27" s="4" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="36" t="n"/>
-      <c r="AC28" s="37" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="AC28" s="7" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="36" t="n"/>
-      <c r="AC29" s="37" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="AC29" s="7" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="36" t="n"/>
-      <c r="AC30" s="37" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="AC30" s="7" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="36" t="n"/>
-      <c r="AC31" s="37" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="AC31" s="7" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="36" t="n"/>
-      <c r="AC32" s="37" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="AC32" s="7" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="36" t="n"/>
-      <c r="AC33" s="37" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="AC33" s="7" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="B34" s="36" t="n"/>
-      <c r="AC34" s="37" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="AC34" s="7" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="38" t="n"/>
-      <c r="C35" s="32" t="n"/>
-      <c r="D35" s="32" t="n"/>
-      <c r="E35" s="32" t="n"/>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="32" t="n"/>
-      <c r="H35" s="32" t="n"/>
-      <c r="I35" s="32" t="n"/>
-      <c r="J35" s="32" t="n"/>
-      <c r="K35" s="32" t="n"/>
-      <c r="L35" s="32" t="n"/>
-      <c r="M35" s="32" t="n"/>
-      <c r="N35" s="32" t="n"/>
-      <c r="O35" s="32" t="n"/>
-      <c r="P35" s="32" t="n"/>
-      <c r="Q35" s="32" t="n"/>
-      <c r="R35" s="32" t="n"/>
-      <c r="S35" s="32" t="n"/>
-      <c r="T35" s="32" t="n"/>
-      <c r="U35" s="32" t="n"/>
-      <c r="V35" s="32" t="n"/>
-      <c r="W35" s="32" t="n"/>
-      <c r="X35" s="32" t="n"/>
-      <c r="Y35" s="32" t="n"/>
-      <c r="Z35" s="32" t="n"/>
-      <c r="AA35" s="32" t="n"/>
-      <c r="AB35" s="32" t="n"/>
-      <c r="AC35" s="39" t="n"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="9" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="9" t="n"/>
+      <c r="S35" s="9" t="n"/>
+      <c r="T35" s="9" t="n"/>
+      <c r="U35" s="9" t="n"/>
+      <c r="V35" s="9" t="n"/>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n"/>
+      <c r="Z35" s="9" t="n"/>
+      <c r="AA35" s="9" t="n"/>
+      <c r="AB35" s="9" t="n"/>
+      <c r="AC35" s="10" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="31" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>■ 業務への示唆</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="32" t="n"/>
-      <c r="C38" s="32" t="n"/>
-      <c r="D38" s="32" t="n"/>
-      <c r="E38" s="32" t="n"/>
-      <c r="F38" s="32" t="n"/>
-      <c r="G38" s="32" t="n"/>
-      <c r="H38" s="32" t="n"/>
-      <c r="I38" s="32" t="n"/>
-      <c r="J38" s="32" t="n"/>
-      <c r="K38" s="32" t="n"/>
-      <c r="L38" s="32" t="n"/>
-      <c r="M38" s="32" t="n"/>
-      <c r="N38" s="32" t="n"/>
-      <c r="O38" s="32" t="n"/>
-      <c r="P38" s="32" t="n"/>
-      <c r="Q38" s="32" t="n"/>
-      <c r="R38" s="32" t="n"/>
-      <c r="S38" s="32" t="n"/>
-      <c r="T38" s="32" t="n"/>
-      <c r="U38" s="32" t="n"/>
-      <c r="V38" s="32" t="n"/>
-      <c r="W38" s="32" t="n"/>
-      <c r="X38" s="32" t="n"/>
-      <c r="Y38" s="32" t="n"/>
-      <c r="Z38" s="32" t="n"/>
-      <c r="AA38" s="32" t="n"/>
-      <c r="AB38" s="32" t="n"/>
-      <c r="AC38" s="32" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
+      <c r="L38" s="9" t="n"/>
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="9" t="n"/>
+      <c r="O38" s="9" t="n"/>
+      <c r="P38" s="9" t="n"/>
+      <c r="Q38" s="9" t="n"/>
+      <c r="R38" s="9" t="n"/>
+      <c r="S38" s="9" t="n"/>
+      <c r="T38" s="9" t="n"/>
+      <c r="U38" s="9" t="n"/>
+      <c r="V38" s="9" t="n"/>
+      <c r="W38" s="9" t="n"/>
+      <c r="X38" s="9" t="n"/>
+      <c r="Y38" s="9" t="n"/>
+      <c r="Z38" s="9" t="n"/>
+      <c r="AA38" s="9" t="n"/>
+      <c r="AB38" s="9" t="n"/>
+      <c r="AC38" s="9" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="33" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>【子供001】
 平均欠席日数は約1.3日と予測された。約5か月後に安定が見込まれるため、それまでは健康観察と家庭との情報共有を継続することが望ましい。
@@ -1959,91 +1959,91 @@
 平均欠席日数は約1.8日と予測された。約9か月後に安定が見込まれるため、それまでは健康観察と家庭との情報共有を継続することが望ましい。</t>
         </is>
       </c>
-      <c r="C39" s="34" t="n"/>
-      <c r="D39" s="34" t="n"/>
-      <c r="E39" s="34" t="n"/>
-      <c r="F39" s="34" t="n"/>
-      <c r="G39" s="34" t="n"/>
-      <c r="H39" s="34" t="n"/>
-      <c r="I39" s="34" t="n"/>
-      <c r="J39" s="34" t="n"/>
-      <c r="K39" s="34" t="n"/>
-      <c r="L39" s="34" t="n"/>
-      <c r="M39" s="34" t="n"/>
-      <c r="N39" s="34" t="n"/>
-      <c r="O39" s="34" t="n"/>
-      <c r="P39" s="34" t="n"/>
-      <c r="Q39" s="34" t="n"/>
-      <c r="R39" s="34" t="n"/>
-      <c r="S39" s="34" t="n"/>
-      <c r="T39" s="34" t="n"/>
-      <c r="U39" s="34" t="n"/>
-      <c r="V39" s="34" t="n"/>
-      <c r="W39" s="34" t="n"/>
-      <c r="X39" s="34" t="n"/>
-      <c r="Y39" s="34" t="n"/>
-      <c r="Z39" s="34" t="n"/>
-      <c r="AA39" s="34" t="n"/>
-      <c r="AB39" s="34" t="n"/>
-      <c r="AC39" s="35" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n"/>
+      <c r="Q39" s="3" t="n"/>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="3" t="n"/>
+      <c r="T39" s="3" t="n"/>
+      <c r="U39" s="3" t="n"/>
+      <c r="V39" s="3" t="n"/>
+      <c r="W39" s="3" t="n"/>
+      <c r="X39" s="3" t="n"/>
+      <c r="Y39" s="3" t="n"/>
+      <c r="Z39" s="3" t="n"/>
+      <c r="AA39" s="3" t="n"/>
+      <c r="AB39" s="3" t="n"/>
+      <c r="AC39" s="4" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="B40" s="36" t="n"/>
-      <c r="AC40" s="37" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="AC40" s="7" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="36" t="n"/>
-      <c r="AC41" s="37" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="AC41" s="7" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="36" t="n"/>
-      <c r="AC42" s="37" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="AC42" s="7" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="36" t="n"/>
-      <c r="AC43" s="37" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="AC43" s="7" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="36" t="n"/>
-      <c r="AC44" s="37" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="AC44" s="7" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="B45" s="36" t="n"/>
-      <c r="AC45" s="37" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="AC45" s="7" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="B46" s="36" t="n"/>
-      <c r="AC46" s="37" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="AC46" s="7" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="B47" s="38" t="n"/>
-      <c r="C47" s="32" t="n"/>
-      <c r="D47" s="32" t="n"/>
-      <c r="E47" s="32" t="n"/>
-      <c r="F47" s="32" t="n"/>
-      <c r="G47" s="32" t="n"/>
-      <c r="H47" s="32" t="n"/>
-      <c r="I47" s="32" t="n"/>
-      <c r="J47" s="32" t="n"/>
-      <c r="K47" s="32" t="n"/>
-      <c r="L47" s="32" t="n"/>
-      <c r="M47" s="32" t="n"/>
-      <c r="N47" s="32" t="n"/>
-      <c r="O47" s="32" t="n"/>
-      <c r="P47" s="32" t="n"/>
-      <c r="Q47" s="32" t="n"/>
-      <c r="R47" s="32" t="n"/>
-      <c r="S47" s="32" t="n"/>
-      <c r="T47" s="32" t="n"/>
-      <c r="U47" s="32" t="n"/>
-      <c r="V47" s="32" t="n"/>
-      <c r="W47" s="32" t="n"/>
-      <c r="X47" s="32" t="n"/>
-      <c r="Y47" s="32" t="n"/>
-      <c r="Z47" s="32" t="n"/>
-      <c r="AA47" s="32" t="n"/>
-      <c r="AB47" s="32" t="n"/>
-      <c r="AC47" s="39" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="9" t="n"/>
+      <c r="L47" s="9" t="n"/>
+      <c r="M47" s="9" t="n"/>
+      <c r="N47" s="9" t="n"/>
+      <c r="O47" s="9" t="n"/>
+      <c r="P47" s="9" t="n"/>
+      <c r="Q47" s="9" t="n"/>
+      <c r="R47" s="9" t="n"/>
+      <c r="S47" s="9" t="n"/>
+      <c r="T47" s="9" t="n"/>
+      <c r="U47" s="9" t="n"/>
+      <c r="V47" s="9" t="n"/>
+      <c r="W47" s="9" t="n"/>
+      <c r="X47" s="9" t="n"/>
+      <c r="Y47" s="9" t="n"/>
+      <c r="Z47" s="9" t="n"/>
+      <c r="AA47" s="9" t="n"/>
+      <c r="AB47" s="9" t="n"/>
+      <c r="AC47" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2069,11 +2069,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-2.分析① 月齢別</t>
         </is>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>2-2.分析② 学年別</t>
         </is>
@@ -2108,11 +2108,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-2.分析③ 登園月数</t>
         </is>
@@ -2120,7 +2120,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>2-2.分析④ 登園年数別</t>
         </is>
@@ -2147,11 +2147,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-2.分析⑤ 月間</t>
         </is>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>2-2.分析⑥ 月別</t>
         </is>
@@ -2186,11 +2186,11 @@
   <dimension ref="B2:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-2.分析 傾向考察</t>
         </is>
@@ -2198,226 +2198,226 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>■ 考察</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="32" t="n"/>
-      <c r="C5" s="32" t="n"/>
-      <c r="D5" s="32" t="n"/>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="32" t="n"/>
-      <c r="G5" s="32" t="n"/>
-      <c r="H5" s="32" t="n"/>
-      <c r="I5" s="32" t="n"/>
-      <c r="J5" s="32" t="n"/>
-      <c r="K5" s="32" t="n"/>
-      <c r="L5" s="32" t="n"/>
-      <c r="M5" s="32" t="n"/>
-      <c r="N5" s="32" t="n"/>
-      <c r="O5" s="32" t="n"/>
-      <c r="P5" s="32" t="n"/>
-      <c r="Q5" s="32" t="n"/>
-      <c r="R5" s="32" t="n"/>
-      <c r="S5" s="32" t="n"/>
-      <c r="T5" s="32" t="n"/>
-      <c r="U5" s="32" t="n"/>
-      <c r="V5" s="32" t="n"/>
-      <c r="W5" s="32" t="n"/>
-      <c r="X5" s="32" t="n"/>
-      <c r="Y5" s="32" t="n"/>
-      <c r="Z5" s="32" t="n"/>
-      <c r="AA5" s="32" t="n"/>
-      <c r="AB5" s="32" t="n"/>
-      <c r="AC5" s="32" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="9" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="9" t="n"/>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="9" t="n"/>
+      <c r="AA5" s="9" t="n"/>
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="9" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>【子供001】
-月齢による平均欠席日数の大きな変化は認められなかった。
-学年が上がるにつれて平均欠席日数は約30.0日から約0.0日へ減少した。
-登園月数の経過に伴い平均欠席日数は約4.0日から約0.0日へ減少した。
-登園年数の経過に伴い平均欠席日数は約31.0日から約0.0日へ減少した。
-8月の平均欠席日数が約19.0日と最も高く、季節性の影響がみられた。
-月間推移では平均欠席日数が約2.0日から約0.0日へ減少した。
+月齢による欠席日数の大きな変化は認められなかった。
+学年が上がるにつれて欠席日数は約30.0日から約0.0日へ減少した。
+登園月数の経過に伴い欠席日数は約4.0日から約0.0日へ減少した。
+登園年数の経過に伴い欠席日数は約31.0日から約0.0日へ減少した。
+8月の欠席日数が約19.0日と最も高く、季節性の影響がみられた。
+月間推移では欠席日数が約2.0日から約0.0日へ減少した。
 【子供002】
-月齢による平均欠席日数の大きな変化は認められなかった。
-学年が上がるにつれて平均欠席日数は約15.0日から約0.0日へ減少した。
-登園月数の経過に伴い平均欠席日数は約2.0日から約0.0日へ減少した。
-登園年数の経過に伴い平均欠席日数は約21.0日から約5.0日へ減少した。
-11月の平均欠席日数が約10.0日と最も高く、季節性の影響がみられた。
-月間推移では平均欠席日数が約2.0日から約0.0日へ減少した。</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n"/>
-      <c r="F6" s="34" t="n"/>
-      <c r="G6" s="34" t="n"/>
-      <c r="H6" s="34" t="n"/>
-      <c r="I6" s="34" t="n"/>
-      <c r="J6" s="34" t="n"/>
-      <c r="K6" s="34" t="n"/>
-      <c r="L6" s="34" t="n"/>
-      <c r="M6" s="34" t="n"/>
-      <c r="N6" s="34" t="n"/>
-      <c r="O6" s="34" t="n"/>
-      <c r="P6" s="34" t="n"/>
-      <c r="Q6" s="34" t="n"/>
-      <c r="R6" s="34" t="n"/>
-      <c r="S6" s="34" t="n"/>
-      <c r="T6" s="34" t="n"/>
-      <c r="U6" s="34" t="n"/>
-      <c r="V6" s="34" t="n"/>
-      <c r="W6" s="34" t="n"/>
-      <c r="X6" s="34" t="n"/>
-      <c r="Y6" s="34" t="n"/>
-      <c r="Z6" s="34" t="n"/>
-      <c r="AA6" s="34" t="n"/>
-      <c r="AB6" s="34" t="n"/>
-      <c r="AC6" s="35" t="n"/>
+月齢による欠席日数の大きな変化は認められなかった。
+学年が上がるにつれて欠席日数は約15.0日から約0.0日へ減少した。
+登園月数の経過に伴い欠席日数は約2.0日から約0.0日へ減少した。
+登園年数の経過に伴い欠席日数は約21.0日から約5.0日へ減少した。
+11月の欠席日数が約10.0日と最も高く、季節性の影響がみられた。
+月間推移では欠席日数が約2.0日から約0.0日へ減少した。</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="3" t="n"/>
+      <c r="X6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n"/>
+      <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" s="4" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="36" t="n"/>
-      <c r="AC7" s="37" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="AC7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="36" t="n"/>
-      <c r="AC8" s="37" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="AC8" s="7" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="36" t="n"/>
-      <c r="AC9" s="37" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="AC9" s="7" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="36" t="n"/>
-      <c r="AC10" s="37" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="AC10" s="7" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="36" t="n"/>
-      <c r="AC11" s="37" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="AC11" s="7" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="B12" s="36" t="n"/>
-      <c r="AC12" s="37" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="AC12" s="7" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="36" t="n"/>
-      <c r="AC13" s="37" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="AC13" s="7" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="36" t="n"/>
-      <c r="AC14" s="37" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="AC14" s="7" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="36" t="n"/>
-      <c r="AC15" s="37" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="AC15" s="7" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="36" t="n"/>
-      <c r="AC16" s="37" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="AC16" s="7" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="36" t="n"/>
-      <c r="AC17" s="37" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="AC17" s="7" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="36" t="n"/>
-      <c r="AC18" s="37" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="AC18" s="7" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="36" t="n"/>
-      <c r="AC19" s="37" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="AC19" s="7" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="36" t="n"/>
-      <c r="AC20" s="37" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="AC20" s="7" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="36" t="n"/>
-      <c r="AC21" s="37" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="AC21" s="7" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="36" t="n"/>
-      <c r="AC22" s="37" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="AC22" s="7" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="36" t="n"/>
-      <c r="AC23" s="37" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="AC23" s="7" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="38" t="n"/>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="32" t="n"/>
-      <c r="F24" s="32" t="n"/>
-      <c r="G24" s="32" t="n"/>
-      <c r="H24" s="32" t="n"/>
-      <c r="I24" s="32" t="n"/>
-      <c r="J24" s="32" t="n"/>
-      <c r="K24" s="32" t="n"/>
-      <c r="L24" s="32" t="n"/>
-      <c r="M24" s="32" t="n"/>
-      <c r="N24" s="32" t="n"/>
-      <c r="O24" s="32" t="n"/>
-      <c r="P24" s="32" t="n"/>
-      <c r="Q24" s="32" t="n"/>
-      <c r="R24" s="32" t="n"/>
-      <c r="S24" s="32" t="n"/>
-      <c r="T24" s="32" t="n"/>
-      <c r="U24" s="32" t="n"/>
-      <c r="V24" s="32" t="n"/>
-      <c r="W24" s="32" t="n"/>
-      <c r="X24" s="32" t="n"/>
-      <c r="Y24" s="32" t="n"/>
-      <c r="Z24" s="32" t="n"/>
-      <c r="AA24" s="32" t="n"/>
-      <c r="AB24" s="32" t="n"/>
-      <c r="AC24" s="39" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="9" t="n"/>
+      <c r="S24" s="9" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="9" t="n"/>
+      <c r="V24" s="9" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="9" t="n"/>
+      <c r="Y24" s="9" t="n"/>
+      <c r="Z24" s="9" t="n"/>
+      <c r="AA24" s="9" t="n"/>
+      <c r="AB24" s="9" t="n"/>
+      <c r="AC24" s="10" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="31" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>■ 業務改善提案</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="B27" s="32" t="n"/>
-      <c r="C27" s="32" t="n"/>
-      <c r="D27" s="32" t="n"/>
-      <c r="E27" s="32" t="n"/>
-      <c r="F27" s="32" t="n"/>
-      <c r="G27" s="32" t="n"/>
-      <c r="H27" s="32" t="n"/>
-      <c r="I27" s="32" t="n"/>
-      <c r="J27" s="32" t="n"/>
-      <c r="K27" s="32" t="n"/>
-      <c r="L27" s="32" t="n"/>
-      <c r="M27" s="32" t="n"/>
-      <c r="N27" s="32" t="n"/>
-      <c r="O27" s="32" t="n"/>
-      <c r="P27" s="32" t="n"/>
-      <c r="Q27" s="32" t="n"/>
-      <c r="R27" s="32" t="n"/>
-      <c r="S27" s="32" t="n"/>
-      <c r="T27" s="32" t="n"/>
-      <c r="U27" s="32" t="n"/>
-      <c r="V27" s="32" t="n"/>
-      <c r="W27" s="32" t="n"/>
-      <c r="X27" s="32" t="n"/>
-      <c r="Y27" s="32" t="n"/>
-      <c r="Z27" s="32" t="n"/>
-      <c r="AA27" s="32" t="n"/>
-      <c r="AB27" s="32" t="n"/>
-      <c r="AC27" s="32" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
+      <c r="L27" s="9" t="n"/>
+      <c r="M27" s="9" t="n"/>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="9" t="n"/>
+      <c r="P27" s="9" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="9" t="n"/>
+      <c r="S27" s="9" t="n"/>
+      <c r="T27" s="9" t="n"/>
+      <c r="U27" s="9" t="n"/>
+      <c r="V27" s="9" t="n"/>
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="9" t="n"/>
+      <c r="Y27" s="9" t="n"/>
+      <c r="Z27" s="9" t="n"/>
+      <c r="AA27" s="9" t="n"/>
+      <c r="AB27" s="9" t="n"/>
+      <c r="AC27" s="9" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="33" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>【子供001】
 平均欠席日数は約1.3日と予測された。約5か月後に安定が見込まれるため、それまでは健康観察と家庭との情報共有を継続することが望ましい。
@@ -2425,127 +2425,127 @@
 平均欠席日数は約1.8日と予測された。約9か月後に安定が見込まれるため、それまでは健康観察と家庭との情報共有を継続することが望ましい。</t>
         </is>
       </c>
-      <c r="C28" s="34" t="n"/>
-      <c r="D28" s="34" t="n"/>
-      <c r="E28" s="34" t="n"/>
-      <c r="F28" s="34" t="n"/>
-      <c r="G28" s="34" t="n"/>
-      <c r="H28" s="34" t="n"/>
-      <c r="I28" s="34" t="n"/>
-      <c r="J28" s="34" t="n"/>
-      <c r="K28" s="34" t="n"/>
-      <c r="L28" s="34" t="n"/>
-      <c r="M28" s="34" t="n"/>
-      <c r="N28" s="34" t="n"/>
-      <c r="O28" s="34" t="n"/>
-      <c r="P28" s="34" t="n"/>
-      <c r="Q28" s="34" t="n"/>
-      <c r="R28" s="34" t="n"/>
-      <c r="S28" s="34" t="n"/>
-      <c r="T28" s="34" t="n"/>
-      <c r="U28" s="34" t="n"/>
-      <c r="V28" s="34" t="n"/>
-      <c r="W28" s="34" t="n"/>
-      <c r="X28" s="34" t="n"/>
-      <c r="Y28" s="34" t="n"/>
-      <c r="Z28" s="34" t="n"/>
-      <c r="AA28" s="34" t="n"/>
-      <c r="AB28" s="34" t="n"/>
-      <c r="AC28" s="35" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3" t="n"/>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="3" t="n"/>
+      <c r="Q28" s="3" t="n"/>
+      <c r="R28" s="3" t="n"/>
+      <c r="S28" s="3" t="n"/>
+      <c r="T28" s="3" t="n"/>
+      <c r="U28" s="3" t="n"/>
+      <c r="V28" s="3" t="n"/>
+      <c r="W28" s="3" t="n"/>
+      <c r="X28" s="3" t="n"/>
+      <c r="Y28" s="3" t="n"/>
+      <c r="Z28" s="3" t="n"/>
+      <c r="AA28" s="3" t="n"/>
+      <c r="AB28" s="3" t="n"/>
+      <c r="AC28" s="4" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="36" t="n"/>
-      <c r="AC29" s="37" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="AC29" s="7" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="36" t="n"/>
-      <c r="AC30" s="37" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="AC30" s="7" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="36" t="n"/>
-      <c r="AC31" s="37" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="AC31" s="7" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="36" t="n"/>
-      <c r="AC32" s="37" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="AC32" s="7" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="36" t="n"/>
-      <c r="AC33" s="37" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="AC33" s="7" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="B34" s="36" t="n"/>
-      <c r="AC34" s="37" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="AC34" s="7" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="36" t="n"/>
-      <c r="AC35" s="37" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="AC35" s="7" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="36" t="n"/>
-      <c r="AC36" s="37" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="AC36" s="7" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="36" t="n"/>
-      <c r="AC37" s="37" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="AC37" s="7" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="36" t="n"/>
-      <c r="AC38" s="37" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="AC38" s="7" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="36" t="n"/>
-      <c r="AC39" s="37" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="AC39" s="7" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="B40" s="36" t="n"/>
-      <c r="AC40" s="37" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="AC40" s="7" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="36" t="n"/>
-      <c r="AC41" s="37" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="AC41" s="7" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="36" t="n"/>
-      <c r="AC42" s="37" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="AC42" s="7" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="36" t="n"/>
-      <c r="AC43" s="37" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="AC43" s="7" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="36" t="n"/>
-      <c r="AC44" s="37" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="AC44" s="7" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="B45" s="38" t="n"/>
-      <c r="C45" s="32" t="n"/>
-      <c r="D45" s="32" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="32" t="n"/>
-      <c r="H45" s="32" t="n"/>
-      <c r="I45" s="32" t="n"/>
-      <c r="J45" s="32" t="n"/>
-      <c r="K45" s="32" t="n"/>
-      <c r="L45" s="32" t="n"/>
-      <c r="M45" s="32" t="n"/>
-      <c r="N45" s="32" t="n"/>
-      <c r="O45" s="32" t="n"/>
-      <c r="P45" s="32" t="n"/>
-      <c r="Q45" s="32" t="n"/>
-      <c r="R45" s="32" t="n"/>
-      <c r="S45" s="32" t="n"/>
-      <c r="T45" s="32" t="n"/>
-      <c r="U45" s="32" t="n"/>
-      <c r="V45" s="32" t="n"/>
-      <c r="W45" s="32" t="n"/>
-      <c r="X45" s="32" t="n"/>
-      <c r="Y45" s="32" t="n"/>
-      <c r="Z45" s="32" t="n"/>
-      <c r="AA45" s="32" t="n"/>
-      <c r="AB45" s="32" t="n"/>
-      <c r="AC45" s="39" t="n"/>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+      <c r="L45" s="9" t="n"/>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="9" t="n"/>
+      <c r="P45" s="9" t="n"/>
+      <c r="Q45" s="9" t="n"/>
+      <c r="R45" s="9" t="n"/>
+      <c r="S45" s="9" t="n"/>
+      <c r="T45" s="9" t="n"/>
+      <c r="U45" s="9" t="n"/>
+      <c r="V45" s="9" t="n"/>
+      <c r="W45" s="9" t="n"/>
+      <c r="X45" s="9" t="n"/>
+      <c r="Y45" s="9" t="n"/>
+      <c r="Z45" s="9" t="n"/>
+      <c r="AA45" s="9" t="n"/>
+      <c r="AB45" s="9" t="n"/>
+      <c r="AC45" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2569,11 +2569,11 @@
   <dimension ref="B2:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-2.分析⑦ 未来リスク</t>
         </is>
